--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_reports/mobile_ui_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_reports/mobile_ui_summary.xlsx
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1546248308414427</v>
+        <v>0.1654255045657358</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Conscientiousness</t>
+          <t>Neuroticism, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.1546, 0.1465, 0.1433</t>
+          <t>0.1654, 0.1411, 0.1384</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>primary_persona, Extraversion, Conscientiousness</t>
+          <t>current_mood, primary_persona, Extraversion</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0355, 0.0309, 0.0277</t>
+          <t>0.0334, 0.0328, 0.0316</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.03547752808433706</v>
+        <v>0.03338474742164872</v>
       </c>
     </row>
     <row r="3">
@@ -531,34 +531,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1632939342843895</v>
+        <v>0.175575704624629</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, Conscientiousness</t>
+          <t>Neuroticism, Conscientiousness, Openness</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.1633, 0.1595, 0.1367</t>
+          <t>0.1756, 0.1385, 0.1377</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>primary_device, Openness, Extraversion</t>
+          <t>Agreeableness, primary_device, primary_persona</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0414, 0.0256, 0.0215</t>
+          <t>0.0389, 0.0389, 0.0291</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.04135348618317817</v>
+        <v>0.03890354667296107</v>
       </c>
     </row>
     <row r="4">
@@ -578,30 +578,30 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1733818332768428</v>
+        <v>0.1644936083843054</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_persona, Conscientiousness</t>
+          <t>Neuroticism, Conscientiousness, Openness</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.1734, 0.1520, 0.1456</t>
+          <t>0.1645, 0.1597, 0.1475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, current_mood</t>
+          <t>Neuroticism, primary_device, Extraversion</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0295, 0.0289, 0.0263</t>
+          <t>0.0308, 0.0226, 0.0203</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.02946579695653979</v>
+        <v>0.03077182763434903</v>
       </c>
     </row>
     <row r="5">
@@ -621,30 +621,30 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1753688720402702</v>
+        <v>0.1634285959043757</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conscientiousness, primary_persona, Neuroticism</t>
+          <t>Conscientiousness, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.1754, 0.1430, 0.1415</t>
+          <t>0.1634, 0.1522, 0.1402</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Agreeableness, Conscientiousness, current_mood</t>
+          <t>current_mood, primary_device, Conscientiousness</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0237, 0.0220, 0.0213</t>
+          <t>0.0218, 0.0197, 0.0188</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.02371277463343708</v>
+        <v>0.02183006711368665</v>
       </c>
     </row>
     <row r="6">
@@ -660,34 +660,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1543263702222125</v>
+        <v>0.171996073879084</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, Conscientiousness</t>
+          <t>Neuroticism, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.1543, 0.1515, 0.1421</t>
+          <t>0.1720, 0.1430, 0.1391</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>primary_device, primary_persona, Extraversion</t>
+          <t>primary_device, primary_persona, current_mood</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0449, 0.0297, 0.0283</t>
+          <t>0.0315, 0.0271, 0.0252</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.04493073745636021</v>
+        <v>0.03150951223570677</v>
       </c>
     </row>
     <row r="7">
@@ -707,30 +707,30 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1682407298905595</v>
+        <v>0.1651365657207518</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Conscientiousness, Extraversion, Neuroticism</t>
+          <t>Conscientiousness, Neuroticism, Extraversion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.1682, 0.1446, 0.1396</t>
+          <t>0.1651, 0.1572, 0.1408</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>current_mood, Agreeableness, primary_device</t>
+          <t>primary_persona, Conscientiousness, primary_device</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0511, 0.0335, 0.0281</t>
+          <t>0.0467, 0.0343, 0.0325</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.05113542234606927</v>
+        <v>0.04671541749956636</v>
       </c>
     </row>
     <row r="8">
@@ -746,34 +746,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1729821141017556</v>
+        <v>0.1641360042788341</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, Extraversion</t>
+          <t>current_mood, Neuroticism, Extraversion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.1730, 0.1482, 0.1445</t>
+          <t>0.1641, 0.1463, 0.1323</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>primary_device, primary_persona, Openness</t>
+          <t>Neuroticism, primary_device, primary_persona</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0533, 0.0339, 0.0300</t>
+          <t>0.0448, 0.0440, 0.0419</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.0532851628336115</v>
+        <v>0.04482279937278525</v>
       </c>
     </row>
     <row r="9">
@@ -793,30 +793,30 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1552991183420361</v>
+        <v>0.1612596853077023</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, current_mood</t>
+          <t>Neuroticism, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.1553, 0.1421, 0.1410</t>
+          <t>0.1613, 0.1402, 0.1360</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Conscientiousness, primary_persona, Openness</t>
+          <t>Extraversion, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0308, 0.0266, 0.0266</t>
+          <t>0.0259, 0.0205, 0.0189</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.0307658410250342</v>
+        <v>0.0258639928405956</v>
       </c>
     </row>
     <row r="10">
@@ -836,30 +836,30 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1633089165970898</v>
+        <v>0.1785808417698981</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, current_mood</t>
+          <t>Neuroticism, Conscientiousness, primary_persona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.1633, 0.1461, 0.1364</t>
+          <t>0.1786, 0.1490, 0.1378</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>primary_persona, Openness, Neuroticism</t>
+          <t>Neuroticism, Openness, current_mood</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0325, 0.0315, 0.0309</t>
+          <t>0.0499, 0.0359, 0.0335</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.03249707758068944</v>
+        <v>0.04985584668767024</v>
       </c>
     </row>
     <row r="11">
@@ -875,34 +875,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1480683053593875</v>
+        <v>0.1424409720450504</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Openness, Extraversion, current_mood</t>
+          <t>current_mood, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.1481, 0.1460, 0.1444</t>
+          <t>0.1424, 0.1419, 0.1392</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>primary_device, Extraversion, primary_persona</t>
+          <t>Openness, primary_device, current_mood</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0513, 0.0393, 0.0330</t>
+          <t>0.0316, 0.0307, 0.0282</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.05132729692284529</v>
+        <v>0.03155657743988236</v>
       </c>
     </row>
     <row r="12">
@@ -922,30 +922,30 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1589016105693498</v>
+        <v>0.1535727242355789</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, Conscientiousness, Openness</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.1589, 0.1409, 0.1383</t>
+          <t>0.1536, 0.1508, 0.1474</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Extraversion, Neuroticism, primary_device</t>
+          <t>Extraversion, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0493, 0.0373, 0.0335</t>
+          <t>0.0414, 0.0351, 0.0316</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.04928554520545893</v>
+        <v>0.04136453319739312</v>
       </c>
     </row>
     <row r="13">
@@ -965,30 +965,30 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1642596312543621</v>
+        <v>0.1650522394304711</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, Conscientiousness</t>
+          <t>Neuroticism, Extraversion, Agreeableness</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.1643, 0.1420, 0.1419</t>
+          <t>0.1651, 0.1455, 0.1412</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>primary_persona, Agreeableness, current_mood</t>
+          <t>Conscientiousness, primary_persona, Neuroticism</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0468, 0.0459, 0.0313</t>
+          <t>0.0418, 0.0378, 0.0286</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.0467966667694255</v>
+        <v>0.04180842022227619</v>
       </c>
     </row>
     <row r="14">
@@ -1004,34 +1004,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1516358121404803</v>
+        <v>0.1608578546875862</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, current_mood</t>
+          <t>Agreeableness, primary_persona, Neuroticism</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.1516, 0.1489, 0.1452</t>
+          <t>0.1609, 0.1463, 0.1453</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, Extraversion</t>
+          <t>primary_device, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0781, 0.0426, 0.0412</t>
+          <t>0.0456, 0.0407, 0.0405</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.07812896262476739</v>
+        <v>0.04557040654893607</v>
       </c>
     </row>
     <row r="15">
@@ -1051,30 +1051,30 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1547788099463741</v>
+        <v>0.170288284218379</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, Openness</t>
+          <t>Neuroticism, Openness, Agreeableness</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.1548, 0.1422, 0.1414</t>
+          <t>0.1703, 0.1441, 0.1414</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, primary_device</t>
+          <t>Neuroticism, primary_device, primary_persona</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0434, 0.0334, 0.0287</t>
+          <t>0.0379, 0.0331, 0.0251</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.04343956370071127</v>
+        <v>0.03794284672896697</v>
       </c>
     </row>
   </sheetData>
